--- a/test-cases/Testcase.xlsx
+++ b/test-cases/Testcase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rujipas Panyachon\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DACE1EB8-C826-49A6-B659-AC4A9F80CED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFF8DD7-A201-4B38-9D97-0ADB4840A828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ACE1F75C-17B4-4D58-A8C7-43715AAFE3F0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{ACE1F75C-17B4-4D58-A8C7-43715AAFE3F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="187">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -441,17 +442,173 @@
   </si>
   <si>
     <t>ได้ข้อมูลเป็น array ว่าง [ ] และ Status 200</t>
+  </si>
+  <si>
+    <t>INT-001</t>
+  </si>
+  <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>POST -&gt; GET</t>
+  </si>
+  <si>
+    <t>สร้างหนังสือใหม่ (POST) แล้วลองเรียกดู (GET) ด้วย ID ที่เพิ่งสร้าง</t>
+  </si>
+  <si>
+    <t>ต้องพบข้อมูลหนังสือที่เพิ่งสร้างและข้อมูลตรงกัน (Status 200)</t>
+  </si>
+  <si>
+    <t>INT-002</t>
+  </si>
+  <si>
+    <t>POST -&gt; POST</t>
+  </si>
+  <si>
+    <t>สร้างหนังสือใหม่ (POST) และทำการยืมหนังสือเล่มนั้นทันที (POST /borrow)</t>
+  </si>
+  <si>
+    <t>ยืมสำเร็จ และสถานะหนังสือต้องเปลี่ยนเป็น "borrowed"</t>
+  </si>
+  <si>
+    <t>INT-003</t>
+  </si>
+  <si>
+    <t>PUT -&gt; GET</t>
+  </si>
+  <si>
+    <t>แก้ไขชื่อหนังสือ (PUT) แล้วลองเรียกดู (GET) อีกครั้ง</t>
+  </si>
+  <si>
+    <t>ข้อมูลที่ดึงมาต้องเป็นชื่อใหม่ที่ถูกอัปเดตแล้ว</t>
+  </si>
+  <si>
+    <t>INT-004</t>
+  </si>
+  <si>
+    <t>DELETE -&gt; GET</t>
+  </si>
+  <si>
+    <t>ลบหนังสือ (DELETE) แล้วลองเรียกดูหนังสือเล่มเดิม (GET)</t>
+  </si>
+  <si>
+    <t>ต้องไม่พบข้อมูล และแจ้งเตือน Not Found (Status 404)</t>
+  </si>
+  <si>
+    <t>INT-005</t>
+  </si>
+  <si>
+    <t>POST -&gt; PUT -&gt; DEL</t>
+  </si>
+  <si>
+    <t>สร้าง -&gt; แก้ไข -&gt; ลบ หนังสือใน Flow เดียวกัน</t>
+  </si>
+  <si>
+    <t>ทุกขั้นตอนทำงานสำเร็จตามลำดับ ไม่มี Error</t>
+  </si>
+  <si>
+    <t>SEC-001</t>
+  </si>
+  <si>
+    <t>ลองใส่ SQL Injection ใน URL Parameter เช่น /api/books/1 OR 1=1</t>
+  </si>
+  <si>
+    <t>ระบบปฏิเสธคำขอ แจ้ง Error ทั่วไป ไม่แสดงข้อมูล Database (400)</t>
+  </si>
+  <si>
+    <t>SEC-002</t>
+  </si>
+  <si>
+    <t>ลองแทรก XSS Payload ในฟิลด์ Author เช่น &lt;img src=x onerror=alert(1)&gt;</t>
+  </si>
+  <si>
+    <t>ระบบต้องกรอง (Sanitize) หรือปฏิเสธข้อมูล (Status 400)</t>
+  </si>
+  <si>
+    <t>SEC-003</t>
+  </si>
+  <si>
+    <t>ส่งคำขอยืมหนังสือโดยแก้ไข Header ลบคำว่า Authorization ออก</t>
+  </si>
+  <si>
+    <t>ระบบปฏิเสธการเข้าถึง แจ้ง Unauthorized (Status 401)</t>
+  </si>
+  <si>
+    <t>SEC-004</t>
+  </si>
+  <si>
+    <t>ส่ง Token ที่ถูกแก้ไขดัดแปลง (Invalid JWT Signature)</t>
+  </si>
+  <si>
+    <t>ระบบตรวจสอบว่า Token ปลอม และปฏิเสธการเข้าถึง (Status 401)</t>
+  </si>
+  <si>
+    <t>SEC-005</t>
+  </si>
+  <si>
+    <t>All Endpoints</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>ส่ง Request โดยตั้งค่า Header Content-Type เป็น text/plain แทน application/json</t>
+  </si>
+  <si>
+    <t>แจ้งเตือน Unsupported Media Type (Status 415) หรือจัดการ Error ได้อย่างเหมาะสม</t>
+  </si>
+  <si>
+    <t>VAL-001</t>
+  </si>
+  <si>
+    <t>ส่ง Body ว่างเปล่า {} ไปสร้างหนังสือ</t>
+  </si>
+  <si>
+    <t>แจ้งเตือน Validation Error ระบุฟิลด์ที่ขาดหาย (Status 400)</t>
+  </si>
+  <si>
+    <t>VAL-002</t>
+  </si>
+  <si>
+    <t>ส่ง ID เป็นค่าติดลบ เช่น /api/books/-5</t>
+  </si>
+  <si>
+    <t>แจ้งเตือน Invalid ID format หรือ Not Found (Status 400/404)</t>
+  </si>
+  <si>
+    <t>VAL-003</t>
+  </si>
+  <si>
+    <t>ส่ง ID เป็นเลขศูนย์ เช่น /api/books/0</t>
+  </si>
+  <si>
+    <t>VAL-004</t>
+  </si>
+  <si>
+    <t>แอบส่งฟิลด์ที่ไม่ได้รับอนุญาตมาด้วย เช่น {"title":"A", "role":"admin"}</t>
+  </si>
+  <si>
+    <t>ระบบต้องละทิ้งฟิลด์ role ไม่นำไปบันทึกลง Database (Status 201)</t>
+  </si>
+  <si>
+    <t>VAL-005</t>
+  </si>
+  <si>
+    <t>ใส่ Query Parameter limit=9999999 เพื่อดึงข้อมูลมหาศาล</t>
+  </si>
+  <si>
+    <t>ระบบต้องจำกัดจำนวนสูงสุด (Pagination Limit) เพื่อป้องกันเซิร์ฟเวอร์ล่ม (Status 200)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -459,14 +616,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -519,11 +676,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -860,16 +1020,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323DA9AE-85AB-47E5-A58C-9251141C31AB}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="12.08203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="25.25" customWidth="1"/>
     <col min="4" max="4" width="54.5" customWidth="1"/>
-    <col min="5" max="5" width="59.375" customWidth="1"/>
+    <col min="5" max="5" width="59.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="17" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -886,7 +1047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="17" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -903,7 +1064,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="17" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -920,7 +1081,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="17" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -937,7 +1098,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="17" thickBot="1">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -954,7 +1115,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="17" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -971,7 +1132,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="17" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -988,7 +1149,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="17" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1005,7 +1166,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="17" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1022,7 +1183,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="17" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1039,7 +1200,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="17" thickBot="1">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -1056,7 +1217,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="17" thickBot="1">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1073,7 +1234,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="17" thickBot="1">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1090,7 +1251,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="17" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1107,7 +1268,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="17" thickBot="1">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -1124,7 +1285,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="17" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -1141,7 +1302,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="17" thickBot="1">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
@@ -1158,7 +1319,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="17" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
@@ -1175,7 +1336,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="17" thickBot="1">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
@@ -1192,7 +1353,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="17" thickBot="1">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -1209,7 +1370,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="17" thickBot="1">
       <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
@@ -1226,7 +1387,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="17" thickBot="1">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
@@ -1243,7 +1404,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="17" thickBot="1">
       <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
@@ -1260,7 +1421,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="17" thickBot="1">
       <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
@@ -1277,7 +1438,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="17" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -1294,7 +1455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="17" thickBot="1">
       <c r="A26" s="2" t="s">
         <v>38</v>
       </c>
@@ -1311,7 +1472,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="17" thickBot="1">
       <c r="A27" s="2" t="s">
         <v>39</v>
       </c>
@@ -1328,7 +1489,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="17" thickBot="1">
       <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
@@ -1345,7 +1506,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="17" thickBot="1">
       <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
@@ -1362,7 +1523,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="17" thickBot="1">
       <c r="A30" s="2" t="s">
         <v>42</v>
       </c>
@@ -1379,7 +1540,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="17" thickBot="1">
       <c r="A31" s="2" t="s">
         <v>43</v>
       </c>
@@ -1396,7 +1557,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="17" thickBot="1">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -1413,7 +1574,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="17" thickBot="1">
       <c r="A33" s="2" t="s">
         <v>45</v>
       </c>
@@ -1430,7 +1591,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="17" thickBot="1">
       <c r="A34" s="2" t="s">
         <v>46</v>
       </c>
@@ -1447,7 +1608,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="17" thickBot="1">
       <c r="A35" s="2" t="s">
         <v>47</v>
       </c>
@@ -1464,7 +1625,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="17" thickBot="1">
       <c r="A36" s="2" t="s">
         <v>48</v>
       </c>
@@ -1481,7 +1642,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="17" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>49</v>
       </c>
@@ -1498,7 +1659,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="17" thickBot="1">
       <c r="A38" s="2" t="s">
         <v>50</v>
       </c>
@@ -1515,7 +1676,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="17" thickBot="1">
       <c r="A39" s="2" t="s">
         <v>51</v>
       </c>
@@ -1532,7 +1693,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="17" thickBot="1">
       <c r="A40" s="2" t="s">
         <v>52</v>
       </c>
@@ -1549,7 +1710,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="17" thickBot="1">
       <c r="A41" s="2" t="s">
         <v>53</v>
       </c>
@@ -1566,7 +1727,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="17" thickBot="1">
       <c r="A42" s="2" t="s">
         <v>54</v>
       </c>
@@ -1583,7 +1744,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="17" thickBot="1">
       <c r="A43" s="2" t="s">
         <v>55</v>
       </c>
@@ -1598,10 +1759,266 @@
       </c>
       <c r="E43" s="2" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17" thickBot="1">
+      <c r="A44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17" thickBot="1">
+      <c r="A45" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17" thickBot="1">
+      <c r="A46" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17" thickBot="1">
+      <c r="A47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17" thickBot="1">
+      <c r="A48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17" thickBot="1">
+      <c r="A49" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="17" thickBot="1">
+      <c r="A50" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="17" thickBot="1">
+      <c r="A51" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="17" thickBot="1">
+      <c r="A52" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="27.5" thickBot="1">
+      <c r="A53" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="17" thickBot="1">
+      <c r="A54" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="17" thickBot="1">
+      <c r="A55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="17" thickBot="1">
+      <c r="A56" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="17" thickBot="1">
+      <c r="A57" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="17" thickBot="1">
+      <c r="A58" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>